--- a/fixErrorAllergyCode/ig/StructureDefinition-fr-allergie-intolerance-document.xlsx
+++ b/fixErrorAllergyCode/ig/StructureDefinition-fr-allergie-intolerance-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="353">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:38:14+00:00</t>
+    <t>2026-03-30T14:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,7 +658,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-allergy-substance</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-allergy-code</t>
   </si>
   <si>
     <t>substance/product:@@ -1017,6 +1017,9 @@
   </si>
   <si>
     <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-allergy-substance</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -5322,7 +5325,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>204</v>
+        <v>315</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5355,7 +5358,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5366,14 +5369,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5395,13 +5398,13 @@
         <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5427,13 +5430,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5451,7 +5454,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -5472,19 +5475,19 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5506,13 +5509,13 @@
         <v>236</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5562,7 +5565,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5577,7 +5580,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5588,10 +5591,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5617,10 +5620,10 @@
         <v>249</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5671,7 +5674,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5692,15 +5695,15 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5726,13 +5729,13 @@
         <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5761,10 +5764,10 @@
         <v>158</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -5782,7 +5785,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5808,10 +5811,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5837,13 +5840,13 @@
         <v>154</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5869,13 +5872,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -5893,7 +5896,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5908,7 +5911,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
@@ -5919,10 +5922,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5948,13 +5951,13 @@
         <v>294</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6004,7 +6007,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
